--- a/docs/downloads/08/tbl_produits_elevage_marovoay_tous.xlsx
+++ b/docs/downloads/08/tbl_produits_elevage_marovoay_tous.xlsx
@@ -472,9 +472,6 @@
           <t>Henan'ondry</t>
         </is>
       </c>
-      <c r="C8">
-        <v>4</v>
-      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -547,9 +544,6 @@
           <t>Henan'ondry</t>
         </is>
       </c>
-      <c r="C13">
-        <v>1</v>
-      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -577,9 +571,6 @@
           <t>Trondro Nompian</t>
         </is>
       </c>
-      <c r="C15">
-        <v>1</v>
-      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -592,9 +583,6 @@
           <t>Vorona</t>
         </is>
       </c>
-      <c r="C16">
-        <v>1</v>
-      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -652,9 +640,6 @@
           <t>Henan'ondry</t>
         </is>
       </c>
-      <c r="C20">
-        <v>2</v>
-      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -757,9 +742,6 @@
           <t>Trondro Nompian</t>
         </is>
       </c>
-      <c r="C27">
-        <v>1</v>
-      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -771,9 +753,6 @@
         <is>
           <t>Vorona</t>
         </is>
-      </c>
-      <c r="C28">
-        <v>1</v>
       </c>
     </row>
     <row r="29">

--- a/docs/downloads/08/tbl_produits_elevage_marovoay_tous.xlsx
+++ b/docs/downloads/08/tbl_produits_elevage_marovoay_tous.xlsx
@@ -374,7 +374,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Marovoay - Ampijoroa</t>
+          <t>Ampijoroa</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -389,7 +389,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Marovoay - Ampijoroa</t>
+          <t>Ampijoroa</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -404,7 +404,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Marovoay - Ampijoroa</t>
+          <t>Ampijoroa</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -419,7 +419,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Marovoay - Ampijoroa</t>
+          <t>Ampijoroa</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -434,7 +434,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Marovoay - Bepako</t>
+          <t>Bepako</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -449,7 +449,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Marovoay - Bepako</t>
+          <t>Bepako</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -464,7 +464,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Marovoay - Bepako</t>
+          <t>Bepako</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -476,7 +476,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Marovoay - Bepako</t>
+          <t>Bepako</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -491,7 +491,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Marovoay - Bepako</t>
+          <t>Bepako</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -506,7 +506,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Marovoay - Madiromiongana</t>
+          <t>Madiromiongana</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -521,7 +521,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Marovoay - Madiromiongana</t>
+          <t>Madiromiongana</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -536,7 +536,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Marovoay - Madiromiongana</t>
+          <t>Madiromiongana</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -548,7 +548,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Marovoay - Madiromiongana</t>
+          <t>Madiromiongana</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -563,7 +563,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Marovoay - Madiromiongana</t>
+          <t>Madiromiongana</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -575,7 +575,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Marovoay - Madiromiongana</t>
+          <t>Madiromiongana</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -587,7 +587,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Marovoay - Madiromiongana</t>
+          <t>Madiromiongana</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -602,7 +602,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Marovoay - Maroala</t>
+          <t>Maroala</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -617,7 +617,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Marovoay - Maroala</t>
+          <t>Maroala</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -632,7 +632,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Marovoay - Maroala</t>
+          <t>Maroala</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -644,7 +644,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Marovoay - Maroala</t>
+          <t>Maroala</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -659,7 +659,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Marovoay - Maroala</t>
+          <t>Maroala</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -674,7 +674,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Marovoay - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -689,7 +689,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Marovoay - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -704,7 +704,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Marovoay - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -719,7 +719,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Marovoay - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -734,7 +734,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Marovoay - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -746,7 +746,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Marovoay - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -758,7 +758,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Marovoay - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
